--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0002T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.79712398199297</v>
+        <v>8.579532647073858</v>
       </c>
       <c r="D2" t="n">
-        <v>53.95499416629812</v>
+        <v>8.767686552023445</v>
       </c>
       <c r="E2" t="n">
-        <v>19.49394439211057</v>
+        <v>3.167765963717969</v>
       </c>
       <c r="F2" t="n">
-        <v>18.52090637403775</v>
+        <v>3.009647285781134</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.91427258415851</v>
+        <v>3.723569294925759</v>
       </c>
       <c r="D3" t="n">
-        <v>24.15651487574403</v>
+        <v>3.925433667308404</v>
       </c>
       <c r="E3" t="n">
-        <v>19.49394439211057</v>
+        <v>3.167765963717969</v>
       </c>
       <c r="F3" t="n">
-        <v>18.52090637403775</v>
+        <v>3.009647285781134</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>34.65393284648071</v>
+        <v>5.631264087553117</v>
       </c>
       <c r="D4" t="n">
-        <v>35.86526186253942</v>
+        <v>5.828105052662656</v>
       </c>
       <c r="E4" t="n">
-        <v>19.49394439211057</v>
+        <v>3.167765963717969</v>
       </c>
       <c r="F4" t="n">
-        <v>18.52090637403775</v>
+        <v>3.009647285781134</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>24.28546788961011</v>
+        <v>3.946388532061644</v>
       </c>
       <c r="D5" t="n">
-        <v>24.35021909726247</v>
+        <v>3.956910603305152</v>
       </c>
       <c r="E5" t="n">
-        <v>19.49394439211057</v>
+        <v>3.167765963717969</v>
       </c>
       <c r="F5" t="n">
-        <v>18.52090637403775</v>
+        <v>3.009647285781134</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>74.42879188679872</v>
+        <v>12.09467868160479</v>
       </c>
       <c r="D6" t="n">
-        <v>72.07808266040378</v>
+        <v>11.71268843231561</v>
       </c>
       <c r="E6" t="n">
-        <v>19.49394439211057</v>
+        <v>3.167765963717969</v>
       </c>
       <c r="F6" t="n">
-        <v>18.52090637403775</v>
+        <v>3.009647285781134</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
